--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25910726.8</v>
+        <v>27691.35</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23772193.2</v>
+        <v>25405.85</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17486073.35</v>
+        <v>18687.74</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10932748.45</v>
+        <v>11684.06</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11854861.6</v>
+        <v>12669.55</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12213862.5</v>
+        <v>13053.22</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12601833.1</v>
+        <v>13467.85</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>16719903.75</v>
+        <v>17868.92</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>73948507</v>
+        <v>79030.36</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>14150800</v>
+        <v>15123.26</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27158695.95</v>
+        <v>29025.08</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10629782.95</v>
+        <v>11360.28</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9307347.140000001</v>
+        <v>9946.959999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12325127.5</v>
+        <v>13172.13</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28101925.32</v>
+        <v>30033.13</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11756109.45</v>
+        <v>12564.01</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10770858.3</v>
+        <v>11511.05</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6790861</v>
+        <v>7257.54</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11936733.6</v>
+        <v>12757.04</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17913665</v>
+        <v>19144.72</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9239263.699999999</v>
+        <v>9874.200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>29091448.05</v>
+        <v>31090.65</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>18399889.6</v>
+        <v>19664.36</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>35686195.2</v>
+        <v>38138.6</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22770405.84</v>
+        <v>24335.22</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6152300</v>
+        <v>6575.1</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>22957675.5</v>
+        <v>24535.36</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>25591938.54</v>
+        <v>27350.65</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7374928.26</v>
+        <v>7881.74</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7450394.5</v>
+        <v>7962.4</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>21840308</v>
+        <v>23341.21</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11177075</v>
+        <v>11945.18</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>25390551.48</v>
+        <v>27135.43</v>
       </c>
     </row>
     <row r="35">
@@ -2582,17 +2582,17 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>25111023.85</v>
+        <v>26836.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3888-661-CM25</t>
+          <t>2292-9277-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,37 +2617,37 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7812796.25</v>
+        <v>12079.76</v>
       </c>
     </row>
     <row r="37">
@@ -2704,17 +2704,17 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>55370140.14</v>
+        <v>59175.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2292-9277-CM25</t>
+          <t>3888-661-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,37 +2739,37 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>11302997.4</v>
+        <v>8349.700000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2826,17 +2826,17 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>27439061.65</v>
+        <v>29324.71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5520-10734-CM25</t>
+          <t>5520-10738-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2876,22 +2876,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10354998.5</v>
+        <v>14447.87</v>
       </c>
     </row>
     <row r="41">
@@ -2948,17 +2948,17 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9831780</v>
+        <v>10507.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5520-10738-CM25</t>
+          <t>5520-10734-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>13518834.35</v>
+        <v>11066.61</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7086586.85</v>
+        <v>7573.59</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>24593509.85</v>
+        <v>26283.61</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9385322.800000001</v>
+        <v>10030.3</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12990816.05</v>
+        <v>13883.56</v>
       </c>
     </row>
     <row r="47">
@@ -3314,17 +3314,17 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6585181.2</v>
+        <v>7037.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5510-122-CM25</t>
+          <t>1460278-223-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,28 +3364,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8055767.05</v>
+        <v>6999.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1460278-223-CM25</t>
+          <t>820-49-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3410,43 +3410,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6549385.15</v>
+        <v>10473.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2385-1072-CM25</t>
+          <t>2409-1784-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3466,42 +3466,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8155218.75</v>
+        <v>10569.83</v>
       </c>
     </row>
     <row r="51">
@@ -3558,17 +3558,17 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11483483</v>
+        <v>12272.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2409-1784-CM25</t>
+          <t>5510-122-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,43 +3593,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9890163.949999999</v>
+        <v>8609.370000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>820-49-CM25</t>
+          <t>1417913-589-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,43 +3654,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9799911.800000001</v>
+        <v>20158.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1417913-589-CM25</t>
+          <t>3474-822-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,28 +3730,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>78.042.830-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>18862553.15</v>
+        <v>22824.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3474-822-CM25</t>
+          <t>692277-123-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,28 +3791,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>21356811</v>
+        <v>41504</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>692277-123-CM25</t>
+          <t>1079516-1465-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,43 +3837,43 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SECCIÓN COMPRAS V ZONA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>38835191.08</v>
+        <v>30265.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079516-1465-CM25</t>
+          <t>1346283-253-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3898,43 +3898,43 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>28318991.4</v>
+        <v>12202.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1346283-253-CM25</t>
+          <t>507428-3993-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,37 +3959,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11417735.98</v>
+        <v>49853.53</v>
       </c>
     </row>
     <row r="59">
@@ -4046,17 +4046,17 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5562009</v>
+        <v>5944.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>507428-3993-CM25</t>
+          <t>2723-3897-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4076,22 +4076,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.072.500-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE BUIN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4107,17 +4107,17 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>46647826.6</v>
+        <v>26661.96</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2723-3897-CM25</t>
+          <t>1079580-493-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,53 +4132,53 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.072.500-2</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BUIN</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>24947530.6</v>
+        <v>9442.639999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2713-1187-CM25</t>
+          <t>1079580-495-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,53 +4193,53 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9317432.25</v>
+        <v>17232.29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1079580-493-CM25</t>
+          <t>507428-3992-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4264,43 +4264,43 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8835452.5</v>
+        <v>62042.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1079580-495-CM25</t>
+          <t>1053139-266-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,48 +4320,48 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>16124211.46</v>
+        <v>35188.73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>507428-3992-CM25</t>
+          <t>5510-125-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4381,48 +4381,48 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>58053456.58</v>
+        <v>58336.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1053139-266-CM25</t>
+          <t>2580-1310-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4442,48 +4442,48 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>32926010.6</v>
+        <v>6382.34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5510-125-CM25</t>
+          <t>1475044-17-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4523,28 +4523,28 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>54584988.9</v>
+        <v>8273.52</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2580-1310-CM25</t>
+          <t>1208129-730-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,43 +4569,43 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5971940.66</v>
+        <v>12244.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1208129-730-CM25</t>
+          <t>1476007-10-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4630,43 +4630,43 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>Servicio Nacional de Reinserción Social Juvenil</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11457170.2</v>
+        <v>27528.92</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1475044-17-CM25</t>
+          <t>1232366-156-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,17 +4717,17 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7741510</v>
+        <v>7569</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1476007-10-CM25</t>
+          <t>1293138-354-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4767,28 +4767,28 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>25758745.1</v>
+        <v>62921.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1232366-156-CM25</t>
+          <t>1216062-1154-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,28 +4828,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Rescatelife limitada </t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.217.441-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7082293.4</v>
+        <v>15141.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1293138-354-CM25</t>
+          <t>1469101-5-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,43 +4874,43 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>58875046</v>
+        <v>14803.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1216062-1154-CM25</t>
+          <t>2675-461-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4930,48 +4930,48 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescatelife limitada </t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.217.441-3</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>14168000</v>
+        <v>5540.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1469101-5-CM25</t>
+          <t>5441-799-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,43 +4996,43 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13851425.75</v>
+        <v>13615.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2675-461-CM25</t>
+          <t>1293138-353-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,43 +5057,43 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5184139.8</v>
+        <v>24222.29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1293138-353-CM25</t>
+          <t>4238-396-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22664740</v>
+        <v>13775.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4238-396-CM25</t>
+          <t>5890-193-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,43 +5179,43 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12889598.05</v>
+        <v>12841.88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5441-799-CM25</t>
+          <t>2854-1691-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,53 +5230,53 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>12739802.04</v>
+        <v>14339.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2854-1691-CM25</t>
+          <t>594965-216-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5296,48 +5296,48 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>13417800.8</v>
+        <v>5740.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>594965-216-CM25</t>
+          <t>5740-485-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5362,159 +5362,37 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5371065</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>5890-193-CM25</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>60.506.000-5</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>12016114.25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>5740-485-CM25</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>61.979.060-k</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>EVENTAIL SPA</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>8064782.6</v>
+        <v>8619.01</v>
       </c>
     </row>
   </sheetData>
